--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/MASSACHUSETTS_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/MASSACHUSETTS_2016.xlsx
@@ -679,7 +679,7 @@
         <v>8</v>
       </c>
       <c r="D18">
-        <v>0.009174311926605505</v>
+        <v>0.009174311926605503</v>
       </c>
     </row>
     <row r="19">
@@ -1561,7 +1561,7 @@
         <v>8</v>
       </c>
       <c r="D67">
-        <v>0.009174311926605505</v>
+        <v>0.009174311926605503</v>
       </c>
     </row>
     <row r="68">
@@ -1633,7 +1633,7 @@
         <v>8</v>
       </c>
       <c r="D71">
-        <v>0.009174311926605505</v>
+        <v>0.009174311926605503</v>
       </c>
     </row>
     <row r="72">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C103">
@@ -4549,7 +4549,7 @@
         <v>8</v>
       </c>
       <c r="D233">
-        <v>0.009174311926605505</v>
+        <v>0.009174311926605503</v>
       </c>
     </row>
     <row r="234">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C310">
